--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -811,694 +811,682 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9976,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9901,0.0003,0.0001,0.0067</t>
-  </si>
-  <si>
-    <t>0.0057,0.0004,0.0012,0.9957</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9960,0.0013,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9849,0.0003,0.0003,0.0104</t>
+  </si>
+  <si>
+    <t>0.2495,0.0015,0.0000,0.7762</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9984,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7475,0.0008,0.2150,0.0004</t>
+  </si>
+  <si>
+    <t>0.0669,0.0017,0.9091,0.0009</t>
+  </si>
+  <si>
+    <t>0.3557,0.0001,0.8421,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0003,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9978,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.1196,0.8910,0.0137,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.9958,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9830,0.0003,0.0089,0.0001</t>
+  </si>
+  <si>
+    <t>0.8000,0.0002,0.2295,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9979,0.0004</t>
+  </si>
+  <si>
+    <t>0.3357,0.0000,0.8265,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0103,0.9880,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9807,0.0040,0.0054,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0022</t>
+  </si>
+  <si>
+    <t>0.0057,0.9628,0.0384,0.0000</t>
+  </si>
+  <si>
+    <t>0.9734,0.0278,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9977,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.0132,0.6380,0.2471,0.0101</t>
+  </si>
+  <si>
+    <t>0.0381,0.0002,0.9536,0.0012</t>
+  </si>
+  <si>
+    <t>0.0025,0.0009,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.4648,0.0001,0.6664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0476,0.1424,0.8406,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9943,0.0193,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9870,0.0011,0.7693</t>
+  </si>
+  <si>
+    <t>0.0012,0.9939,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0127,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0002,0.9964,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0030,0.9995,0.0001</t>
+  </si>
+  <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
+    <t>0.9985,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0025,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9873,0.2980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0082,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0019,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3555,0.0003,0.7690,0.0001</t>
+  </si>
+  <si>
+    <t>0.3676,0.0022,0.6294,0.0014</t>
+  </si>
+  <si>
+    <t>0.0021,0.0030,0.9942,0.0053</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.7265,0.7129,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.0499,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9897,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0194,0.9962</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0008,0.9993</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0033,0.9982</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0141,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9834,0.8729,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.3470,0.9856,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.6315,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9056,0.8368,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0037,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0024,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0022,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.0016,0.9920,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0023,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9985,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9979,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9967,0.0060,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.6418,0.4853,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7170,0.0081,0.1872,0.0008</t>
+  </si>
+  <si>
+    <t>0.9783,0.0047,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.1562,0.0757,0.2642,0.0202</t>
+  </si>
+  <si>
+    <t>0.0254,0.0059,0.9659,0.0010</t>
+  </si>
+  <si>
+    <t>0.0104,0.5174,0.0067,0.7100</t>
+  </si>
+  <si>
+    <t>0.0012,0.9977,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9727,0.9431,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7801,0.2210,0.0150,0.0026</t>
+  </si>
+  <si>
+    <t>0.4621,0.5707,0.0046,0.0010</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0016,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7054,0.9832,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8035,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0041,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0083,0.0024,0.9920,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1677,0.0002,0.8430,0.0019</t>
+  </si>
+  <si>
+    <t>0.3292,0.0001,0.8464,0.0001</t>
+  </si>
+  <si>
+    <t>0.9858,0.0003,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.0500,0.0007,0.0003,0.9798</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9871,0.0000</t>
+  </si>
+  <si>
+    <t>0.2364,0.7724,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.6013,0.4132,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.4107,0.0000,0.0010,0.6386</t>
+  </si>
+  <si>
+    <t>0.0004,0.0030,0.9990,0.0007</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.3772,0.5373,0.0160,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.9881,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9717,0.0124,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8460,0.2028,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9458,0.0709,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.1404,0.8949,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9284,0.0726,0.0067,0.0023</t>
+  </si>
+  <si>
+    <t>0.9765,0.0241,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0037,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0036,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9865,0.0049,0.0027,0.0044</t>
+  </si>
+  <si>
+    <t>0.0001,0.0138,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0207,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0031,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0119,0.0005,0.9829,0.0008</t>
+  </si>
+  <si>
+    <t>0.0088,0.0024,0.9914,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0339,0.0732,0.7854,0.0005</t>
+  </si>
+  <si>
+    <t>0.5644,0.0019,0.3479,0.0005</t>
+  </si>
+  <si>
+    <t>0.9890,0.0014,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0545,0.0016,0.9598,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.9965,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9973,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9524,0.0738,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7042,0.4420,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.9919,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0035,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9782,0.0010,0.0034,0.0029</t>
+  </si>
+  <si>
+    <t>0.9400,0.0067,0.0194,0.0016</t>
+  </si>
+  <si>
+    <t>0.9694,0.0035,0.0086,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.0010,0.9930,0.0037</t>
+  </si>
+  <si>
+    <t>0.0024,0.0040,0.9872,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0062,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0099,0.0001,0.9913,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.9186,0.3633,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9904,0.0014,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0645,0.0002,0.9613,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9940,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0729,0.9254,0.0148,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9828,0.0002,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.3114,0.0011,0.6682,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9991,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0088,0.0001,0.9935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0919,0.0001,0.9443,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9994,0.0030</t>
-  </si>
-  <si>
-    <t>0.0064,0.9935,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9911,0.0083,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0010</t>
-  </si>
-  <si>
-    <t>0.0022,0.6653,0.7693,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1510,0.0025,0.8412,0.0005</t>
-  </si>
-  <si>
-    <t>0.0351,0.9663,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.9926,0.0433,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.8059,0.4095,0.0036</t>
-  </si>
-  <si>
-    <t>0.2572,0.0020,0.5966,0.0056</t>
-  </si>
-  <si>
-    <t>0.0010,0.0028,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.9124,0.0000,0.1606,0.0000</t>
-  </si>
-  <si>
-    <t>0.0079,0.0109,0.9875,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9973,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9666,0.0012,0.9014</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.0002,0.9988,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0266,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0703,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9802,0.0094,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0031,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9765,0.0309,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9923,0.6798,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0038,0.9933,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0144,0.0012,0.9815,0.0017</t>
-  </si>
-  <si>
-    <t>0.0005,0.0045,0.9987,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9942,0.2422,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.0224,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9865,0.0000</t>
-  </si>
-  <si>
-    <t>0.0219,0.0004,0.0690,0.9354</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0007,0.9992</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0007,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.3255,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9914,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9822,0.0670,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4184,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.8801,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0186,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9920,0.0112,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0042,0.9954,0.0001</t>
-  </si>
-  <si>
-    <t>0.9656,0.0004,0.0174,0.0012</t>
-  </si>
-  <si>
-    <t>0.0064,0.0000,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0386,0.9723,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9968,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.6589,0.3820,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.8337,0.0020,0.1032,0.0008</t>
-  </si>
-  <si>
-    <t>0.9223,0.0172,0.0206,0.0003</t>
-  </si>
-  <si>
-    <t>0.0250,0.7836,0.0470,0.0079</t>
-  </si>
-  <si>
-    <t>0.0855,0.0152,0.8798,0.0056</t>
-  </si>
-  <si>
-    <t>0.0936,0.2676,0.0035,0.5917</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9983,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.9853,0.0834,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9981,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9363,0.0616,0.0080,0.0018</t>
-  </si>
-  <si>
-    <t>0.7265,0.2961,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.1520,0.9900,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.3941,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0116,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0125,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1621,0.0004,0.8102,0.0019</t>
-  </si>
-  <si>
-    <t>0.6386,0.0000,0.6478,0.0000</t>
-  </si>
-  <si>
-    <t>0.6586,0.0001,0.4729,0.0002</t>
-  </si>
-  <si>
-    <t>0.1987,0.0010,0.0003,0.9170</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.9719,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.9910,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0205,0.9815,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0539,0.0000,0.0023,0.9610</t>
-  </si>
-  <si>
-    <t>0.0004,0.0062,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0000,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.5680,0.4632,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0365,0.9581,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.5455,0.0420,0.2213,0.0025</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0016,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0076,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9293,0.0836,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.6292,0.4639,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.4601,0.1396,0.2682,0.0024</t>
-  </si>
-  <si>
-    <t>0.9964,0.0034,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9812,0.0158,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9972,0.0009,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8922,0.0986,0.0127,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9563,0.0111,0.0164,0.0076</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0012,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0002,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0107,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0016,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0000,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.0001,0.9934,0.0002</t>
-  </si>
-  <si>
-    <t>0.3692,0.0004,0.7995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0603,0.0030,0.9259,0.0015</t>
-  </si>
-  <si>
-    <t>0.1200,0.1261,0.4966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.8422,0.2608,0.0005</t>
-  </si>
-  <si>
-    <t>0.3406,0.0059,0.5053,0.0007</t>
-  </si>
-  <si>
-    <t>0.9501,0.0017,0.0195,0.0014</t>
-  </si>
-  <si>
-    <t>0.9311,0.0010,0.0747,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.9937,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.1333,0.9255,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9765,0.0408,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1177,0.9148,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.9869,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9766,0.0041,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9761,0.0033,0.0016,0.0039</t>
-  </si>
-  <si>
-    <t>0.9537,0.0012,0.0257,0.0007</t>
-  </si>
-  <si>
-    <t>0.7012,0.0007,0.2749,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0007,0.9968,0.0049</t>
-  </si>
-  <si>
-    <t>0.0005,0.0063,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0098,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.0004,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.6029,0.8580,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9829,0.0197,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0038,0.0009,0.0004</t>
+    <t>0.9933,0.0062,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9990,0.0008,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0162,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0246,0.8647,0.1308,0.0005</t>
-  </si>
-  <si>
-    <t>0.9448,0.0009,0.0226,0.0011</t>
-  </si>
-  <si>
-    <t>0.0041,0.0001,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0010,0.9983,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.0272,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0091,0.0167,0.9754,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.9947,0.0002,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9726,0.0001,0.0223,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0127,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0013,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0174,0.0016,0.9635,0.0044</t>
-  </si>
-  <si>
-    <t>0.0180,0.0016,0.9761,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9983,0.0006</t>
-  </si>
-  <si>
-    <t>0.9133,0.0008,0.0004,0.0499</t>
-  </si>
-  <si>
-    <t>0.1985,0.0091,0.0002,0.8780</t>
-  </si>
-  <si>
-    <t>0.0087,0.0001,0.0003,0.9968</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0002</t>
+    <t>0.9949,0.0030,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.0031,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0247,0.0465,0.9003,0.0011</t>
+  </si>
+  <si>
+    <t>0.8467,0.0004,0.1069,0.0003</t>
+  </si>
+  <si>
+    <t>0.1648,0.0001,0.8910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0055,0.9982,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.0375,0.9837,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9971,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.0003,0.9927,0.0013</t>
+  </si>
+  <si>
+    <t>0.9839,0.0005,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.0504,0.0001,0.9720,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0030,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0153,0.0227,0.9377,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0033,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0128,0.9912,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.9926,0.0019</t>
+  </si>
+  <si>
+    <t>0.0192,0.0050,0.9696,0.0008</t>
+  </si>
+  <si>
+    <t>0.0074,0.0029,0.9783,0.0028</t>
+  </si>
+  <si>
+    <t>0.9895,0.0001,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.0067,0.0069,0.0000,0.9972</t>
+  </si>
+  <si>
+    <t>0.0030,0.0000,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0002,0.0004</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1926,7 +1914,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1954,7 +1942,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1968,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1982,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2010,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2052,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,7 +2068,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2138,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2203,10 +2191,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2250,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,7 +2278,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,7 +2292,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2329,10 +2317,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2357,10 +2345,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2371,10 +2359,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,7 +2390,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2441,10 +2429,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2446,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,7 +2488,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2735,10 +2723,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2833,10 +2821,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2866,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2889,10 +2877,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2906,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2920,7 +2908,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2964,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2978,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +2992,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3006,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3020,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,10 +3031,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3048,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3062,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,10 +3073,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3102,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3116,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3270,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3328,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3454,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3468,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,7 +3482,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,10 +3493,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,7 +3510,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3533,10 +3521,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3589,10 +3577,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,10 +3619,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,7 +3745,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>385</v>
@@ -3771,7 +3759,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>386</v>
@@ -3900,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3942,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3981,7 +3969,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>399</v>
@@ -3998,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>357</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,7 +4000,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4079,10 +4067,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4124,7 +4112,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4264,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4303,7 +4291,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>417</v>
@@ -4348,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4555,10 +4543,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4569,10 +4557,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,10 +4571,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4588,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4599,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4616,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4656,7 +4644,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,10 +4655,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4714,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,7 +4728,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4784,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4821,10 +4809,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4961,10 +4949,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>325</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5104,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,10 +5103,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>479</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>297</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5316,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5412,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>493</v>
+        <v>394</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5440,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
